--- a/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DCFC42-0F4A-4D8C-8B83-FA2285F8755D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AB420E-A748-469F-86A5-1DE982A7E375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>output_title</t>
   </si>
@@ -94,9 +94,6 @@
     <t>age_months_histogram_overall_unweighted</t>
   </si>
   <si>
-    <t>age_months_distribution_unweighted</t>
-  </si>
-  <si>
     <t>age_months</t>
   </si>
   <si>
@@ -109,18 +106,12 @@
     <t>age_months_histogram_overall_weighted</t>
   </si>
   <si>
-    <t>age_months_distribution_weighted</t>
-  </si>
-  <si>
     <t>year_or_month="month", age_months_col=@variable_map$age_months,weighted=TRUE,weights_col=@variable_map$weight,breaks=1</t>
   </si>
   <si>
     <t>age_months_cat_donut_overall_unweighted</t>
   </si>
   <si>
-    <t>age_months_cat_donut_unweighted</t>
-  </si>
-  <si>
     <t>age_months_cat</t>
   </si>
   <si>
@@ -133,9 +124,6 @@
     <t>age_months_cat_donut_overall_weighted</t>
   </si>
   <si>
-    <t>age_months_cat_donut_weighted</t>
-  </si>
-  <si>
     <t>category_var=@variable_map$age_months_cat,weighted=TRUE,weights_col=@variable_map$weight,variable_label=@variable_label$age_months_cat</t>
   </si>
   <si>
@@ -184,9 +172,6 @@
     <t>age_cat_by_sex_demo_table</t>
   </si>
   <si>
-    <t>sex_age_cat_demo_table</t>
-  </si>
-  <si>
     <t>sex,age_cat</t>
   </si>
   <si>
@@ -196,9 +181,6 @@
     <t>age_months_cat_by_sex_demo_table</t>
   </si>
   <si>
-    <t>sex_age_months_cat_demo_table</t>
-  </si>
-  <si>
     <t>sex,age_months_cat</t>
   </si>
   <si>
@@ -206,6 +188,42 @@
   </si>
   <si>
     <t>base</t>
+  </si>
+  <si>
+    <t>age_pyramid_overall_unweighted1</t>
+  </si>
+  <si>
+    <t>age_pyramid_overall_weighted2</t>
+  </si>
+  <si>
+    <t>age_months_distribution_unweighted3</t>
+  </si>
+  <si>
+    <t>age_months_distribution_weighted4</t>
+  </si>
+  <si>
+    <t>age_months_cat_donut_unweighted5</t>
+  </si>
+  <si>
+    <t>age_months_cat_donut_weighted6</t>
+  </si>
+  <si>
+    <t>basic_demo_table7</t>
+  </si>
+  <si>
+    <t>basic_demo_table_strata8</t>
+  </si>
+  <si>
+    <t>basic_demo_table_weighted9</t>
+  </si>
+  <si>
+    <t>basic_demo_table_strata_weighted10</t>
+  </si>
+  <si>
+    <t>sex_age_cat_demo_table11</t>
+  </si>
+  <si>
+    <t>sex_age_months_cat_demo_table12</t>
   </si>
 </sst>
 </file>
@@ -652,7 +670,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -670,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -678,7 +696,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -696,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -704,16 +722,16 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -722,24 +740,24 @@
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -748,24 +766,24 @@
         <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -774,24 +792,24 @@
         <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -800,163 +818,163 @@
         <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
         <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>43</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
